--- a/data/entrada/docencia/titulaciones actividad centro.xlsx
+++ b/data/entrada/docencia/titulaciones actividad centro.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarzal/_Activo/eco/CoAna/data/entrada/docencia/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73941380-1137-2049-85C0-D992DCE4B7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="33060" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="310">
   <si>
     <t>tipo</t>
   </si>
@@ -731,19 +737,239 @@
   </si>
   <si>
     <t>máster-geoespacial</t>
+  </si>
+  <si>
+    <t>Grau en Administració i Direcció d'Empreses (Pla de 2024)</t>
+  </si>
+  <si>
+    <t>Grau en Dret (Pla de 2024)</t>
+  </si>
+  <si>
+    <t>Doble Grau en Administració d'Empreses i Dret</t>
+  </si>
+  <si>
+    <t>Grau en Turisme (Pla de 2023)</t>
+  </si>
+  <si>
+    <t>Grau en Arquitectura Tècnica (Pla de 2020)</t>
+  </si>
+  <si>
+    <t>Grau en Economia (Pla de 2024)</t>
+  </si>
+  <si>
+    <t>Grau en Finances i Comptabilitat (Pla de 2024)</t>
+  </si>
+  <si>
+    <t>Programa de Màster Transversal en Ciència i Tecnologia</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Advocacia i Procura</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Traducció Medicosanitària (Pla de 2013)</t>
+  </si>
+  <si>
+    <t>Grau en Química (Pla de 2025)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Innovació en Comunicació (Pla de 2025)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Cooperació al Desenvolupament (Pla de 2015) (A distància)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Rehabilitació Psicosocial en Salut Mental Comunitària (Pla de 2025)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Direcció d'Empreses (Pla de 2022) / Master in Management (2022 Programme of Study)</t>
+  </si>
+  <si>
+    <t>Grau en Disseny i Desenvolupament de Videojocs (Pla de 2025)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Sostenibilitat i Responsabilitat Social Corporativa (Pla de 2017)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Estudis Internacionals de Pau, Conflictes i Desenvolupament (Pla de 2025)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Gestió Administrativa</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Psicopedagogia (Pla de 2025)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Estudis Internacionals de Pau, Conflictes i Desenvolupament (Pla de 2013)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Llengua Anglesa per al Comerç Internacional (Pla de 2025) / Master in English Language for International Trade (2025 Programme of Study)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Investigació Aplicada en Estudis Feministes, de Gènere i Ciutadania (Pla de 2022)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Ensenyament i Adquisició de la Llengua Anglesa en Contextos Multilingües (Pla de 2025)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Prevenció de Riscos Laborals (Pla de 2025)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Comunicació Intercultural i Ensenyament de Llengües (Pla de 2025)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Psicologia del Treball, de les Organitzacions i en Recursos Humans (Pla de 2025) (Presencial)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Disseny i Fabricació (Pla de 2024)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Igualtat i Gènere en l'Àmbit Públic i Privat (Pla de 2013)</t>
+  </si>
+  <si>
+    <t>Màster Universitari Erasmus Mundus en Robòtica Intel·ligent Marina i Marítima (Pla de 2024)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Sistemes Intel·ligents (Pla de 2023)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Psicologia del Treball, de les Organitzacions i en Recursos Humans (Pla de 2025) (Virtual)</t>
+  </si>
+  <si>
+    <t>Grau en Economia de l'Empresa Internacional / Bachelor in International Business Economics</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Química Aplicada i Farmacològica (Pla de 2025)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Matemàtica Computacional (Pla de 2013) (Presencial)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Matemàtica Computacional (Pla de 2013) (A distància)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Química Teòrica i Modelització Computacional (Pla de 2021)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Gestió Financera i Comptabilitat Avançada (Pla de 2013)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Intervenció i Mediació Familiar (Pla de 2014)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Eficiència Energètica i Sostenibilitat (Pla de 2024)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Investigació en Traducció i Interpretació (Pla de 2025) / Master in Researching Translation and Interpreting (2025 Programme of Study)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Cooperació al Desenvolupament (Pla de 2025)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Sistema de Justícia Penal</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Història de l'Art i Cultura Visual</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Eficiència Energètica i Sostenibilitat (Pla de 2018)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Advocacia</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Comunicació Intercultural i Ensenyament de Llengües (Pla de 2013)</t>
+  </si>
+  <si>
+    <t>Doble Grau en Mestre o Mestra en Educació Infantil i Primària</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Psicologia del Treball, de les Organitzacions i en Recursos Humans (Pla de 2014) (Presencial)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Ensenyament i Adquisició de la Llengua Anglesa en Contextos Multilingües (Pla de 2013) (A distància)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Psicologia del Treball, de les Organitzacions i en Recursos Humans (Pla de 2014) (A distància)</t>
+  </si>
+  <si>
+    <t>Màster Universitari en Noves Tendències i Processos d'Innovació en Comunicació (Pla de 2016)</t>
+  </si>
+  <si>
+    <t>Doble Grau en Administració i Direcció d'Empreses i Dret (Pla de 2024)</t>
+  </si>
+  <si>
+    <t>doble-grado-ade-derecho</t>
+  </si>
+  <si>
+    <t>máster-mentira</t>
+  </si>
+  <si>
+    <t>máster-abogacía</t>
+  </si>
+  <si>
+    <t>máster-cooperación-desarrollo</t>
+  </si>
+  <si>
+    <t>máster-gestión-administrativa</t>
+  </si>
+  <si>
+    <t>máster-género</t>
+  </si>
+  <si>
+    <t>máster-igualdad-género</t>
+  </si>
+  <si>
+    <t>grado-economía-internacional</t>
+  </si>
+  <si>
+    <t>máster-química-teórica</t>
+  </si>
+  <si>
+    <t>máster-penal</t>
+  </si>
+  <si>
+    <t>máster-historia-arte</t>
+  </si>
+  <si>
+    <t>doble-grado-maestro-infantil-primaria</t>
+  </si>
+  <si>
+    <t>Programa de doctorat en Estudis Internacionals en Pau, Conflictes i Desenvolupament</t>
+  </si>
+  <si>
+    <t>Programa de doctorat en Dret</t>
+  </si>
+  <si>
+    <t>Programa de doctorat en Llengües Aplicades, Literatura i Traducció</t>
+  </si>
+  <si>
+    <t>Grau en Enginyeria Agroalimentària i del Medi Rural</t>
+  </si>
+  <si>
+    <t>Programa de doctorat en Química Sostenible</t>
+  </si>
+  <si>
+    <t>Programa de doctorat en Ciències de la Comunicació (Programa 2022)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -769,7 +995,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -777,40 +1003,58 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
-    <dxf/>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
+      <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:G107" totalsRowShown="0">
-  <autoFilter ref="A1:G107"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Frame0" displayName="Frame0" ref="A1:G166" totalsRowShown="0">
+  <autoFilter ref="A1:G166" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G166">
+    <sortCondition ref="B1:B166"/>
+  </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="tipo" dataDxfId="0"/>
-    <tableColumn id="2" name="titulación" dataDxfId="1"/>
-    <tableColumn id="3" name="nombre" dataDxfId="0"/>
-    <tableColumn id="4" name="cargos_que_la_usan" dataDxfId="0"/>
-    <tableColumn id="5" name="n_personas" dataDxfId="1"/>
-    <tableColumn id="6" name="actividad" dataDxfId="0"/>
-    <tableColumn id="7" name="centro" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="tipo"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="titulación" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="nombre"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="cargos_que_la_usan"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="n_personas" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="actividad"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="centro"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -848,7 +1092,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -882,6 +1126,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -916,9 +1161,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1091,11 +1337,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G107"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G166"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41" customWidth="1"/>
+    <col min="4" max="4" width="27.1640625" customWidth="1"/>
+    <col min="6" max="6" width="31.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1118,7 +1370,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1141,7 +1393,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1164,7 +1416,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1187,7 +1439,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1210,7 +1462,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1233,7 +1485,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1256,7 +1508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1279,7 +1531,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -1302,7 +1554,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1325,7 +1577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1348,7 +1600,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1371,7 +1623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -1394,7 +1646,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -1417,7 +1669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
@@ -1440,7 +1692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
@@ -1463,7 +1715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
@@ -1486,7 +1738,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
@@ -1509,7 +1761,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
@@ -1532,7 +1784,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -1555,7 +1807,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -1578,7 +1830,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -1601,7 +1853,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -1624,7 +1876,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -1647,7 +1899,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -1670,7 +1922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -1693,7 +1945,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -1716,820 +1968,758 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B28" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>74</v>
+        <v>307</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="2">
-        <v>6</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E28" s="2"/>
       <c r="F28" s="1" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B29" s="2">
+        <v>228</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="2">
+        <v>6</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="2">
         <v>229</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E30" s="2">
         <v>8</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="2">
-        <v>230</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" s="2">
-        <v>9</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B31" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E31" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="2">
+        <v>231</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="2">
+        <v>7</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G32" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2">
         <v>232</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E33" s="2">
         <v>5</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="2">
         <v>233</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E34" s="2">
         <v>2</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="2">
-        <v>234</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="2">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B35" s="2">
+        <v>234</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="2">
         <v>235</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E35" s="2">
-        <v>7</v>
-      </c>
-      <c r="F35" s="1" t="s">
+      <c r="E36" s="2">
+        <v>7</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="2">
+        <v>236</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" t="s">
+        <v>292</v>
+      </c>
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="2">
         <v>237</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E38" s="2">
         <v>9</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="2">
         <v>238</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E39" s="2">
         <v>8</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="2">
-        <v>239</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E38" s="2">
-        <v>3</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="2">
-        <v>240</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E39" s="2">
-        <v>6</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B40" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B41" s="2">
+        <v>240</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="2">
+        <v>6</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="2">
+        <v>241</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E41" s="2">
-        <v>3</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="2">
-        <v>244</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E42" s="2">
-        <v>6</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G42" s="1" t="s">
+      <c r="E42" s="3"/>
+      <c r="F42" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B43" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E43" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B44" s="2">
+        <v>243</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" s="2">
+        <v>3</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="2">
+        <v>244</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" s="2">
+        <v>6</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="2">
+        <v>245</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" s="2">
+        <v>5</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="2">
+        <v>246</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="2">
         <v>247</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="2">
-        <v>1</v>
-      </c>
-      <c r="F44" s="1" t="s">
+      <c r="E48" s="2">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" s="2">
-        <v>249</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="2">
-        <v>1</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="2">
-        <v>253</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E46" s="2">
-        <v>1</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="2">
-        <v>258</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E47" s="2">
-        <v>2</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="2">
-        <v>259</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E48" s="2">
-        <v>3</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B49" s="2">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B50" s="2">
-        <v>14101</v>
+        <v>250</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E50" s="2">
-        <v>1</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>239</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" t="s">
+        <v>38</v>
+      </c>
+      <c r="G50" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B51" s="2">
-        <v>14102</v>
+        <v>251</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E51" s="2">
-        <v>1</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>244</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" t="s">
+        <v>41</v>
+      </c>
+      <c r="G51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B52" s="2">
-        <v>14104</v>
+        <v>252</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E52" s="2">
-        <v>1</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>245</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" t="s">
+        <v>43</v>
+      </c>
+      <c r="G52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B53" s="2">
-        <v>14105</v>
+        <v>253</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E53" s="2">
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B54" s="2">
-        <v>14111</v>
+        <v>254</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E54" s="2">
-        <v>1</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>240</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" t="s">
+        <v>45</v>
+      </c>
+      <c r="G54" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B55" s="2">
-        <v>14112</v>
+        <v>255</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E55" s="2">
-        <v>1</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>291</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" t="s">
+        <v>292</v>
+      </c>
+      <c r="G55" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B56" s="2">
-        <v>14113</v>
+        <v>256</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E56" s="2">
-        <v>1</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>254</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B57" s="2">
-        <v>14115</v>
+        <v>257</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E57" s="2">
-        <v>1</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>271</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" t="s">
+        <v>299</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B58" s="2">
-        <v>14116</v>
+        <v>258</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="E58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B59" s="2">
-        <v>14118</v>
+        <v>259</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="E59" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B60" s="2">
-        <v>14119</v>
+        <v>260</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="E60" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B61" s="2">
-        <v>14120</v>
+        <v>261</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E61" s="2">
-        <v>1</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>249</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" t="s">
+        <v>34</v>
+      </c>
+      <c r="G61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="B62" s="2">
-        <v>14122</v>
+        <v>262</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E62" s="2">
-        <v>1</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>286</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" t="s">
+        <v>303</v>
+      </c>
+      <c r="G62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B63" s="2">
-        <v>14123</v>
+        <v>14101</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>115</v>
@@ -2538,21 +2728,21 @@
         <v>1</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B64" s="2">
-        <v>14124</v>
+        <v>14102</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>115</v>
@@ -2561,21 +2751,21 @@
         <v>1</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B65" s="2">
-        <v>14127</v>
+        <v>14104</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>115</v>
@@ -2584,21 +2774,21 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B66" s="2">
-        <v>14128</v>
+        <v>14105</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>115</v>
@@ -2607,21 +2797,21 @@
         <v>1</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B67" s="2">
-        <v>14130</v>
+        <v>14106</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>151</v>
+        <v>304</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>115</v>
@@ -2630,21 +2820,21 @@
         <v>1</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B68" s="2">
-        <v>14131</v>
+        <v>14108</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>153</v>
+        <v>305</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>115</v>
@@ -2653,21 +2843,21 @@
         <v>1</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B69" s="2">
-        <v>14132</v>
+        <v>14110</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>155</v>
+        <v>306</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>115</v>
@@ -2676,21 +2866,21 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B70" s="2">
-        <v>14133</v>
+        <v>14111</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>115</v>
@@ -2699,21 +2889,21 @@
         <v>1</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B71" s="2">
-        <v>14135</v>
+        <v>14112</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>115</v>
@@ -2722,21 +2912,21 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B72" s="2">
-        <v>14138</v>
+        <v>14113</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>115</v>
@@ -2745,44 +2935,44 @@
         <v>1</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B73" s="2">
-        <v>14140</v>
+        <v>14114</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>163</v>
+        <v>308</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="E73" s="2">
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B74" s="2">
-        <v>14141</v>
+        <v>14115</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>115</v>
@@ -2791,481 +2981,481 @@
         <v>1</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="B75" s="2">
+        <v>14116</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E75" s="2">
+        <v>1</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B76" s="2">
+        <v>14118</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E76" s="2">
+        <v>1</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B77" s="2">
+        <v>14119</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E77" s="2">
+        <v>1</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B78" s="2">
+        <v>14120</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E78" s="2">
+        <v>1</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B79" s="2">
+        <v>14122</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E79" s="2">
+        <v>1</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B80" s="2">
+        <v>14123</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E80" s="2">
+        <v>1</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B81" s="2">
+        <v>14124</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E81" s="2">
+        <v>1</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B82" s="2">
+        <v>14127</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E82" s="2">
+        <v>1</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B83" s="2">
+        <v>14128</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E83" s="2">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B84" s="2">
+        <v>14130</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E84" s="2">
+        <v>1</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B85" s="2">
+        <v>14131</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E85" s="2">
+        <v>1</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B86" s="2">
+        <v>14132</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E86" s="2">
+        <v>1</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B87" s="2">
+        <v>14133</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E87" s="2">
+        <v>1</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B88" s="2">
+        <v>14134</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E88" s="2">
+        <v>1</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89" s="2">
+        <v>14135</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E89" s="2">
+        <v>1</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B90" s="2">
+        <v>14138</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E90" s="2">
+        <v>1</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B91" s="2">
+        <v>14140</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E91" s="2">
+        <v>1</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B92" s="2">
+        <v>14141</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E92" s="2">
+        <v>1</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B93" s="2">
         <v>42102</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E75" s="2">
-        <v>1</v>
-      </c>
-      <c r="F75" s="1" t="s">
+      <c r="E93" s="2">
+        <v>1</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="G93" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B76" s="2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B94" s="2">
         <v>42103</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E76" s="2">
-        <v>1</v>
-      </c>
-      <c r="F76" s="1" t="s">
+      <c r="E94" s="2">
+        <v>1</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="G94" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B77" s="2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B95" s="2">
         <v>42106</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E77" s="2">
-        <v>1</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B78" s="2">
-        <v>42110</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E78" s="2">
-        <v>1</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B79" s="2">
-        <v>42111</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E79" s="2">
-        <v>2</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B80" s="2">
-        <v>42112</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E80" s="2">
-        <v>1</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B81" s="2">
-        <v>42114</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E81" s="2">
-        <v>1</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B82" s="2">
-        <v>42119</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E82" s="2">
-        <v>1</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B83" s="2">
-        <v>42120</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E83" s="2">
-        <v>1</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B84" s="2">
-        <v>42121</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E84" s="2">
-        <v>1</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B85" s="2">
-        <v>42129</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E85" s="2">
-        <v>1</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B86" s="2">
-        <v>42134</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E86" s="2">
-        <v>1</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B87" s="2">
-        <v>42135</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E87" s="2">
-        <v>1</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B88" s="2">
-        <v>42139</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E88" s="2">
-        <v>2</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B89" s="2">
-        <v>42142</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E89" s="2">
-        <v>1</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B90" s="2">
-        <v>42150</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E90" s="2">
-        <v>1</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B91" s="2">
-        <v>42151</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E91" s="2">
-        <v>1</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B92" s="2">
-        <v>42157</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E92" s="2">
-        <v>1</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B93" s="2">
-        <v>42159</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E93" s="2">
-        <v>1</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B94" s="2">
-        <v>42163</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E94" s="2">
-        <v>1</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B95" s="2">
-        <v>42164</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>175</v>
@@ -3274,136 +3464,136 @@
         <v>1</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>167</v>
       </c>
       <c r="B96" s="2">
-        <v>42173</v>
+        <v>42110</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E96" s="2">
+        <v>1</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B97" s="2">
+        <v>42111</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E97" s="2">
+        <v>2</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B98" s="2">
+        <v>42112</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E96" s="2">
-        <v>1</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B97" s="2">
-        <v>42175</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D97" s="1" t="s">
+      <c r="E98" s="2">
+        <v>1</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B99" s="2">
+        <v>42114</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E99" s="2">
+        <v>1</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B100" s="2">
+        <v>42119</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E97" s="2">
-        <v>1</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B98" s="2">
-        <v>42179</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E98" s="2">
-        <v>1</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B99" s="2">
-        <v>42180</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E99" s="2">
-        <v>1</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B100" s="2">
-        <v>42184</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E100" s="2">
         <v>1</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>167</v>
       </c>
       <c r="B101" s="2">
-        <v>42185</v>
+        <v>42120</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>175</v>
@@ -3412,44 +3602,44 @@
         <v>1</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>167</v>
       </c>
       <c r="B102" s="2">
-        <v>42196</v>
+        <v>42121</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E102" s="2">
         <v>1</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>167</v>
       </c>
       <c r="B103" s="2">
-        <v>42198</v>
+        <v>42129</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>175</v>
@@ -3458,106 +3648,1259 @@
         <v>1</v>
       </c>
       <c r="F103" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B104" s="2">
+        <v>42134</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E104" s="2">
+        <v>1</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B105" s="2">
+        <v>42135</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E105" s="2">
+        <v>1</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B106" s="2">
+        <v>42139</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E106" s="2">
+        <v>2</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B107" s="2">
+        <v>42142</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E107" s="2">
+        <v>1</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B108" s="2">
+        <v>42145</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E108" s="3"/>
+      <c r="F108" t="s">
+        <v>302</v>
+      </c>
+      <c r="G108" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B109" s="2">
+        <v>42146</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E109" s="3"/>
+      <c r="F109" t="s">
+        <v>301</v>
+      </c>
+      <c r="G109" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B110" s="2">
+        <v>42150</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E110" s="2">
+        <v>1</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B111" s="2">
+        <v>42151</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E111" s="2">
+        <v>1</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B112" s="2">
+        <v>42152</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E112" s="3"/>
+      <c r="F112" t="s">
+        <v>294</v>
+      </c>
+      <c r="G112" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B113" s="2">
+        <v>42154</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E113" s="3"/>
+      <c r="F113" t="s">
+        <v>176</v>
+      </c>
+      <c r="G113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B114" s="2">
+        <v>42155</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E114" s="3"/>
+      <c r="F114" t="s">
+        <v>194</v>
+      </c>
+      <c r="G114" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B115" s="2">
+        <v>42157</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E115" s="2">
+        <v>1</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B116" s="2">
+        <v>42159</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E116" s="2">
+        <v>1</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B117" s="2">
+        <v>42163</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E117" s="2">
+        <v>1</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B118" s="2">
+        <v>42164</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E118" s="2">
+        <v>1</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B119" s="2">
+        <v>42166</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E119" s="3"/>
+      <c r="F119" t="s">
+        <v>188</v>
+      </c>
+      <c r="G119" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B120" s="2">
+        <v>42168</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E120" s="3"/>
+      <c r="F120" t="s">
+        <v>196</v>
+      </c>
+      <c r="G120" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B121" s="2">
+        <v>42169</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E121" s="3"/>
+      <c r="F121" t="s">
+        <v>298</v>
+      </c>
+      <c r="G121" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B122" s="2">
+        <v>42171</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E122" s="3"/>
+      <c r="F122" t="s">
+        <v>181</v>
+      </c>
+      <c r="G122" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B123" s="2">
+        <v>42172</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E123" s="3"/>
+      <c r="F123" t="s">
+        <v>192</v>
+      </c>
+      <c r="G123" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B124" s="2">
+        <v>42173</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E124" s="2">
+        <v>1</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B125" s="2">
+        <v>42175</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E125" s="2">
+        <v>1</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B126" s="2">
+        <v>42177</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E126" s="3"/>
+      <c r="F126" t="s">
+        <v>173</v>
+      </c>
+      <c r="G126" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A127" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B127" s="2">
+        <v>42179</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E127" s="2">
+        <v>1</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B128" s="2">
+        <v>42180</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E128" s="2">
+        <v>1</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B129" s="2">
+        <v>42184</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E129" s="2">
+        <v>1</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B130" s="2">
+        <v>42185</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E130" s="2">
+        <v>1</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B131" s="2">
+        <v>42192</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E131" s="3"/>
+      <c r="F131" t="s">
+        <v>190</v>
+      </c>
+      <c r="G131" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B132" s="2">
+        <v>42194</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E132" s="3"/>
+      <c r="F132" t="s">
+        <v>186</v>
+      </c>
+      <c r="G132" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B133" s="2">
+        <v>42195</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E133" s="3"/>
+      <c r="F133" t="s">
+        <v>183</v>
+      </c>
+      <c r="G133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B134" s="2">
+        <v>42196</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E134" s="2">
+        <v>1</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B135" s="2">
+        <v>42198</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E135" s="2">
+        <v>1</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="G103" s="1" t="s">
+      <c r="G135" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
-      <c r="A104" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B104" s="2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B136" s="2">
         <v>42199</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C136" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E104" s="2">
-        <v>1</v>
-      </c>
-      <c r="F104" s="1" t="s">
+      <c r="E136" s="2">
+        <v>1</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G104" s="1" t="s">
+      <c r="G136" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
-      <c r="A105" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B105" s="2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B137" s="2">
         <v>42200</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C137" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D137" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E105" s="2">
-        <v>1</v>
-      </c>
-      <c r="F105" s="1" t="s">
+      <c r="E137" s="2">
+        <v>1</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="G137" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
-      <c r="A106" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B106" s="2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B138" s="2">
         <v>42202</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C138" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D138" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E106" s="2">
-        <v>1</v>
-      </c>
-      <c r="F106" s="1" t="s">
+      <c r="E138" s="2">
+        <v>1</v>
+      </c>
+      <c r="F138" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="G106" s="1" t="s">
+      <c r="G138" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
-      <c r="A107" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B107" s="2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B139" s="2">
+        <v>42203</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E139" s="3"/>
+      <c r="F139" t="s">
+        <v>300</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B140" s="2">
+        <v>42204</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E140" s="3"/>
+      <c r="F140" t="s">
+        <v>226</v>
+      </c>
+      <c r="G140" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B141" s="2">
+        <v>42206</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E141" s="3"/>
+      <c r="F141" t="s">
+        <v>297</v>
+      </c>
+      <c r="G141" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B142" s="2">
         <v>42207</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C142" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D142" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E107" s="2">
-        <v>1</v>
-      </c>
-      <c r="F107" s="1" t="s">
+      <c r="E142" s="2">
+        <v>1</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="G107" s="1" t="s">
+      <c r="G142" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B143" s="2">
+        <v>42208</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E143" s="3"/>
+      <c r="F143" t="s">
+        <v>210</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B144" s="2">
+        <v>42210</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E144" s="3"/>
+      <c r="F144" t="s">
+        <v>294</v>
+      </c>
+      <c r="G144" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B145" s="2">
+        <v>42211</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E145" s="3"/>
+      <c r="F145" t="s">
+        <v>183</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B146" s="2">
+        <v>42212</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E146" s="3"/>
+      <c r="F146" t="s">
+        <v>178</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B147" s="2">
+        <v>42213</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E147" s="3"/>
+      <c r="F147" t="s">
+        <v>232</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B148" s="2">
+        <v>42214</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E148" s="3"/>
+      <c r="F148" t="s">
+        <v>295</v>
+      </c>
+      <c r="G148" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B149" s="2">
+        <v>42215</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E149" s="3"/>
+      <c r="F149" t="s">
+        <v>196</v>
+      </c>
+      <c r="G149" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B150" s="2">
+        <v>42216</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E150" s="3"/>
+      <c r="F150" t="s">
+        <v>214</v>
+      </c>
+      <c r="G150" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B151" s="2">
+        <v>42217</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E151" s="3"/>
+      <c r="F151" t="s">
+        <v>173</v>
+      </c>
+      <c r="G151" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B152" s="2">
+        <v>42218</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E152" s="3"/>
+      <c r="F152" t="s">
+        <v>296</v>
+      </c>
+      <c r="G152" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B153" s="2">
+        <v>42219</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E153" s="3"/>
+      <c r="F153" t="s">
+        <v>190</v>
+      </c>
+      <c r="G153" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B154" s="2">
+        <v>42220</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E154" s="3"/>
+      <c r="F154" t="s">
+        <v>222</v>
+      </c>
+      <c r="G154" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B155" s="2">
+        <v>42221</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E155" s="3"/>
+      <c r="F155" t="s">
+        <v>202</v>
+      </c>
+      <c r="G155" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B156" s="2">
+        <v>42222</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E156" s="3"/>
+      <c r="F156" t="s">
+        <v>208</v>
+      </c>
+      <c r="G156" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B157" s="2">
+        <v>42223</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E157" s="3"/>
+      <c r="F157" t="s">
+        <v>204</v>
+      </c>
+      <c r="G157" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B158" s="2">
+        <v>42224</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E158" s="3"/>
+      <c r="F158" t="s">
+        <v>200</v>
+      </c>
+      <c r="G158" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B159" s="2">
+        <v>42225</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E159" s="3"/>
+      <c r="F159" t="s">
+        <v>206</v>
+      </c>
+      <c r="G159" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B160" s="2">
+        <v>42292</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E160" s="3"/>
+      <c r="F160" t="s">
+        <v>192</v>
+      </c>
+      <c r="G160" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B161" s="2">
+        <v>42554</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E161" s="3"/>
+      <c r="F161" t="s">
+        <v>176</v>
+      </c>
+      <c r="G161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B162" s="2">
+        <v>42564</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E162" s="3"/>
+      <c r="F162" t="s">
+        <v>214</v>
+      </c>
+      <c r="G162" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B163" s="2">
+        <v>42572</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E163" s="3"/>
+      <c r="F163" t="s">
+        <v>192</v>
+      </c>
+      <c r="G163" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B164" s="2">
+        <v>42591</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E164" s="3"/>
+      <c r="F164" t="s">
+        <v>295</v>
+      </c>
+      <c r="G164" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A165" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B165" s="2">
+        <v>42592</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E165" s="3"/>
+      <c r="F165" t="s">
+        <v>192</v>
+      </c>
+      <c r="G165" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A166" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B166" s="2">
+        <v>49900</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E166" s="3"/>
+      <c r="F166" t="s">
+        <v>293</v>
+      </c>
+      <c r="G166" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
